--- a/docs/NEST_MATCH_OUTREACH_MASTER_2026-08-20.xlsx
+++ b/docs/NEST_MATCH_OUTREACH_MASTER_2026-08-20.xlsx
@@ -20,6 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Categories" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Freelancer Categories" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Week 1 Provider Outreach" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Company Providers'!$A$1:$T$27</definedName>
@@ -31845,6 +31846,379 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Monday 31 August to Sunday 6 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Service providers only</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Channels</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LinkedIn led, WhatsApp fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15 live verified provider profiles from 30 approaches</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Category breadth target</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>At least 8 different service categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Primary metric</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Live verified profiles, not messages sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pre-send blocker 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Walk provider registration end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pre-send blocker 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fix multi-category profile: one primary plus two additional categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pre-send blocker 3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fix Damiano LinkedIn headline, featured link and first About lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Pre-send blocker 4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sort provider list into Tier A/B/C</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Providers Lux Oasis currently pays; WhatsApp first; 70-80% expected conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tier B</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Providers used before or recommended; WhatsApp or LinkedIn; 40-50% expected conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tier C</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Known companies not used; LinkedIn only; 15-20% expected conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Open item</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Decide founding-provider free-until date before external messages</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Open item</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Write one-page verification standard before using verified heavily</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Open item</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Use ORL profile only as a test; disclose common ownership or set to draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Approval rule</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>No WhatsApp, LinkedIn DM, public post or external send without Damiano approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Main block</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Second block</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Mon 31 Aug</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Registration test, category fix, LinkedIn profile, tier list</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>8 Tier A WhatsApp messages</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tue 1 Sep</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>8 Tier A/B WhatsApp messages</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LinkedIn post and comment replies</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Wed 2 Sep</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10 Tier C LinkedIn connection requests</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DM acceptances and build profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Thu 3 Sep</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Day 3 follow-ups</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8 more LinkedIn requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fri 4 Sep</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DMs to acceptances</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Build profiles and chase trade licences</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sat 5 Sep</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Phone calls to Tier A replied-but-not-registered contacts</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Build profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sun 6 Sep</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Numbers review only</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Draft Week 2 operator post</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/NEST_MATCH_OUTREACH_MASTER_2026-08-20.xlsx
+++ b/docs/NEST_MATCH_OUTREACH_MASTER_2026-08-20.xlsx
@@ -21,6 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Freelancer Categories" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Week 1 Provider Outreach" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LinkedIn Provider Seeds" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Company Providers'!$A$1:$T$27</definedName>
@@ -37,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +52,14 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -80,10 +89,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -103,9 +113,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Headline 4" xfId="1" builtinId="19" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -32077,7 +32089,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -32211,6 +32222,3660 @@
       <c r="C27" t="inlineStr">
         <is>
           <t>Draft Week 2 operator post</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="53" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="37" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="53" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="56" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Provider Type</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Name / Search</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>LinkedIn URL</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cleaning / housekeeping / services marketplace</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Justlife</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/justlife/</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.justlife.com/ae-en/</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Cleaning, laundry, maintenance, home services</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Services marketplace / provider source</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ServiceMarket</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/servicemarket/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://servicemarket.com/</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Good aggregator/source for provider-side recruiting</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Home services / cleaning / maintenance</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Urban Company</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/urbancompany/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.urbancompany.com/dubai</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Large provider network, not Dubai-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Facilities management / maintenance</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mplus</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mplus/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.mplus.ae/</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Maintenance, AC, plumbing, electrical, home care</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Maintenance / technical / handyman</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Hitches &amp; Glitches</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hitches-and-glitches/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.hitchesandglitches.com/</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Strong STR maintenance fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Maintenance / technical / handyman</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>We Will Fix It</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wewillfixit/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.wewillfixit.com/</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Home maintenance and emergency technical work</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Maintenance / technical / handyman</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fixperts</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fixperts/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Need service/geography verification before message</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Facilities management / home services</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Transguard Living</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/transguard-living/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.transguardliving.com/</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Home maintenance, cleaning and move services</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cleaning / indoor health / AC duct / mattress</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>The Healthy Home</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-healthy-home/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://thehealthyhome.me/</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Mattress, sofa, carpet, AC duct and disinfection</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Laundry / linen</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Washmen</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/washmen/</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.washmen.com/</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Laundry route, possible linen partner</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Laundry / dry cleaning</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Laundryheap</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/laundryheap/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.laundryheap.com/ae/</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Laundry route, global company with UAE service</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Moving / relocation / logistics</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Move One</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/move-one/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.moveoneinc.com/</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Relocation and logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Storage / moving / logistics</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>The Box</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-box/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://theboxme.com/</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Storage, moving, warehousing</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Interior design / furnishing / styling</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Zen Interiors</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/zen-interiors/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.zeninteriors.net/</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Interior and furnishing route</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Interior design / architecture</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bishop Design</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bishop-design/</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://bishopdesign.ae/</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Interior/design studio</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Interior design / fit-out</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Designsmith</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/designsmith/</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://designsmith.ae/</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Design/fit-out route</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Luxury interior design / architecture</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Antonovich Group</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/luxury-antonovich-design/</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://antonovich-design.ae/</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>High-end, likely later than cleaning/maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pest control / hygiene</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Rentokil Boecker</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boecker-public-health/</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.boecker.com/</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Pest control, hygiene and public health</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pest control</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>National Pest Control</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/national-pest-control/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.natpest.com/</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Pest control route</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Facilities management / maintenance</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Imdaad</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/imdaad/</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.imdaad.ae/</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Large FM company, may be too enterprise but credible</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cleaning / facilities</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Dubai Clean</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dubai-clean/</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Needs website/contact verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Maintenance / technical</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Maintenance Plus</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maintenance-plus/</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Needs website/contact verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Facilities management</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Dussmann Gulf</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dussmann-gulf/</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.dussmann.ae/</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Cleaning/FM, enterprise profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Facilities management</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ServeU</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/serve-u/</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.serveu.ae/</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>FM and technical services</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Facilities management / technical</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Khansaheb Facilities Management</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/khansaheb-facilities-management/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://khansahebfm.com/</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>FM and technical services</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Facilities management</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EFS Facilities Services</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/efs-facilities-services-group/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://efsme.com/</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Large FM, likely enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cleaning / maintenance</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Spectrum Services</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spectrum-services/</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Needs verification before personalised outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Moving / property clearance</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Take My Junk UAE</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/takemyjunkuae/</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://takemyjunkuae.com/</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Junk/furniture removal, property clearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Security / access control / systems</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SIBCA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sibca/</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.sibca.com/</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Security, fire, ELV and access control</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Real estate law / legal</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Al Tamimi &amp; Company</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/al-tamimi-&amp;-company/</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.tamimi.com/</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Legal route, later priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mortgage / finance</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Holo</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/holohome/</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.useholo.com/</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Mortgage broker / proptech finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mortgage / finance</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Mortgage Finder</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mortgage-finder/</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.mortgagefinder.ae/</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Mortgage broker route</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Valuation / advisory</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ValuStrat</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/valustrat/</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://valustrat.com/</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Valuation and market advisory</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Valuation / consultancy / inspection</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Cavendish Maxwell</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cavendish-maxwell/</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://cavendishmaxwell.com/</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Valuation, advisory, property services</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Business setup / PRO / licensing</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Creative Zone</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/creative-zone/</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.creativezone.ae/</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Business setup, licensing, PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Business setup / PRO / licensing</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Virtuzone</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/virtuzone/</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://virtuzone.com/</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Business setup and corporate services</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>STR operator / guest operations benchmark</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>GuestReady</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/guestready/</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.guestready.com/</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Operator-side, benchmark not provider-first</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>STR operator / guest operations benchmark</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Maison Privee</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maison-privee/</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.maisonprivee.ae/</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Operator-side, benchmark not provider-first</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PMS / technology provider</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Hostaway</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hostaway/</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.hostaway.com/</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Global/UAE users</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>PMS/channel technology partner</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Revenue management / dynamic pricing</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PriceLabs</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pricelabs/</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://hello.pricelabs.co/</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Global/UAE users</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Dynamic pricing/revenue management</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PMS / technology provider</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Guesty</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/guesty/</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://www.guesty.com/</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Global/UAE users</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>PMS/channel technology partner</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Channel management / hotel tech</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SiteMinder</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/siteminder/</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.siteminder.com/</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Global/UAE users</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Distribution/channel manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>STR market data</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AirDNA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/airdna/</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://www.airdna.co/</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Global/UAE data</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>STR data partner, later priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Tadbeer / domestic worker services</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Tadbeer</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tadbeer/</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://tadbeer.gov.ae/</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Only relevant if legal/domestic staffing route opens</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Short-term rental operator / flexible living</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Silkhaus</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/silkhaus/</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://www.silkhaus.com/</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Operator benchmark, not provider-first</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Flexible living / furnished apartments</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Blueground</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/blueground-co/</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.theblueground.com/</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dubai/UAE</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Live LinkedIn company URL checked by HTTP 200</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Operator benchmark, not provider-first</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Freelance property manager</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Freelance Property Manager Dubai</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Property%20Manager%20Dubai</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Freelance guest relations / concierge</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Freelance Guest Relations Dubai holiday homes</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Guest%20Relations%20Dubai%20holiday%20homes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Freelance check-in agent</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Freelance Check In Agent Dubai Airbnb</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Check%20In%20Agent%20Dubai%20Airbnb</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Freelance operations assistant</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Freelance Operations Assistant Dubai holiday homes</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Operations%20Assistant%20Dubai%20holiday%20homes</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Freelance revenue manager</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Freelance Revenue Manager Dubai short term rental</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Revenue%20Manager%20Dubai%20short%20term%20rental</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Freelance pricing strategist</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Freelance Pricing Strategist Dubai Airbnb</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Pricing%20Strategist%20Dubai%20Airbnb</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Freelance channel manager</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Freelance Channel Manager Dubai hospitality</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Channel%20Manager%20Dubai%20hospitality</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Freelance cleaner / housekeeper</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Freelance Cleaner Dubai holiday homes</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Cleaner%20Dubai%20holiday%20homes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Freelance handyman</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Freelance Handyman Dubai property maintenance</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Handyman%20Dubai%20property%20maintenance</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Freelance AC technician</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Freelance AC Technician Dubai</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20AC%20Technician%20Dubai</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Freelance plumber</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Freelance Plumber Dubai</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Plumber%20Dubai</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Freelance electrician</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Freelance Electrician Dubai</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Electrician%20Dubai</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Freelance smart lock technician</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Freelance Smart Lock Technician Dubai Airbnb</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Smart%20Lock%20Technician%20Dubai%20Airbnb</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Freelance carpenter / joiner</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Freelance Carpenter Dubai joinery</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Carpenter%20Dubai%20joinery</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Freelance interior designer / stager</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Freelance Interior Designer Dubai home staging</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Interior%20Designer%20Dubai%20home%20staging</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Freelance photographer</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Freelance Real Estate Photographer Dubai</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Real%20Estate%20Photographer%20Dubai</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Freelance videographer / drone operator</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Freelance Drone Videographer Dubai real estate</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Drone%20Videographer%20Dubai%20real%20estate</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Freelance Wi-Fi / IT technician</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Freelance WiFi IT Technician Dubai apartments</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20WiFi%20IT%20Technician%20Dubai%20apartments</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Freelance pool technician / gardener</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Freelance Pool Technician Dubai villa</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Pool%20Technician%20Dubai%20villa</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Freelance driver / chauffeur</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Freelance Chauffeur Driver Dubai</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Chauffeur%20Driver%20Dubai</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Freelance DTCM / licensing consultant</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Freelance DTCM Consultant Dubai holiday homes</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20DTCM%20Consultant%20Dubai%20holiday%20homes</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Freelance accountant / VAT consultant</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Freelance Accountant VAT Dubai property</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Accountant%20VAT%20Dubai%20property</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Freelance legal / conveyancing</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Freelance Conveyancing Consultant Dubai real estate</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Conveyancing%20Consultant%20Dubai%20real%20estate</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Freelance mortgage broker</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Freelance Mortgage Broker Dubai</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Mortgage%20Broker%20Dubai</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Freelancer search</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Freelance business development / acquisitions</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Freelance Property Acquisition Specialist Dubai</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Freelance%20Property%20Acquisition%20Specialist%20Dubai</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>LinkedIn people-search route, login may be required</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Use to find individual profiles, then qualify manually</t>
         </is>
       </c>
     </row>
